--- a/Design Files/LogNController/BOM/eSpark BOM.xlsx
+++ b/Design Files/LogNController/BOM/eSpark BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="370">
   <si>
     <t>Component list</t>
   </si>
@@ -1050,9 +1050,6 @@
     <t>Focus LCDs</t>
   </si>
   <si>
-    <t>Focus LCD</t>
-  </si>
-  <si>
     <t>LCD Display</t>
   </si>
   <si>
@@ -1099,6 +1096,39 @@
   </si>
   <si>
     <t>Digital pH Sensor</t>
+  </si>
+  <si>
+    <t>DC Pump</t>
+  </si>
+  <si>
+    <t>Button Caps</t>
+  </si>
+  <si>
+    <t>KTSC-22I</t>
+  </si>
+  <si>
+    <t>AC Pump</t>
+  </si>
+  <si>
+    <t>Switch Accessories / Caps ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diptronics </t>
+  </si>
+  <si>
+    <t>7A108</t>
+  </si>
+  <si>
+    <t>1.2 GPM Pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bayite </t>
+  </si>
+  <si>
+    <t>Alternate 1.5GPM version selected</t>
+  </si>
+  <si>
+    <t>Chipsmall</t>
   </si>
 </sst>
 </file>
@@ -1537,17 +1567,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1571,6 +1590,17 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1914,7 +1944,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -1922,7 +1952,7 @@
     <col min="4" max="4" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
@@ -1946,13 +1976,13 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
     </row>
     <row r="2" spans="1:17" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1975,7 +2005,7 @@
       <c r="N2" s="30"/>
       <c r="O2" s="30"/>
       <c r="P2" s="30"/>
-      <c r="Q2" s="39"/>
+      <c r="Q2" s="36"/>
     </row>
     <row r="3" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -1998,7 +2028,7 @@
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
       <c r="P3" s="22"/>
-      <c r="Q3" s="40"/>
+      <c r="Q3" s="37"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2017,7 +2047,7 @@
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
       <c r="P4" s="22"/>
-      <c r="Q4" s="40"/>
+      <c r="Q4" s="37"/>
     </row>
     <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2036,26 +2066,26 @@
       <c r="N5" s="33"/>
       <c r="O5" s="33"/>
       <c r="P5" s="33"/>
-      <c r="Q5" s="41"/>
+      <c r="Q5" s="38"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="48"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="45"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -2147,7 +2177,7 @@
       <c r="M8" s="13">
         <v>1</v>
       </c>
-      <c r="N8" s="49" t="s">
+      <c r="N8" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O8" s="14">
@@ -2162,7 +2192,7 @@
     <row r="9" spans="1:17" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="16">
-        <f t="shared" ref="B9:B67" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B70" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -2196,7 +2226,7 @@
       <c r="M9" s="18">
         <v>100</v>
       </c>
-      <c r="N9" s="49" t="s">
+      <c r="N9" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O9" s="19">
@@ -2245,7 +2275,7 @@
       <c r="M10" s="13">
         <v>20</v>
       </c>
-      <c r="N10" s="49" t="s">
+      <c r="N10" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O10" s="14">
@@ -2294,7 +2324,7 @@
       <c r="M11" s="18">
         <v>5</v>
       </c>
-      <c r="N11" s="49" t="s">
+      <c r="N11" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O11" s="19">
@@ -2343,7 +2373,7 @@
       <c r="M12" s="13">
         <v>10</v>
       </c>
-      <c r="N12" s="49" t="s">
+      <c r="N12" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O12" s="14">
@@ -2392,7 +2422,7 @@
       <c r="M13" s="18">
         <v>100</v>
       </c>
-      <c r="N13" s="49" t="s">
+      <c r="N13" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O13" s="19">
@@ -2441,7 +2471,7 @@
       <c r="M14" s="13">
         <v>20</v>
       </c>
-      <c r="N14" s="49" t="s">
+      <c r="N14" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O14" s="14">
@@ -2490,7 +2520,7 @@
       <c r="M15" s="18">
         <v>50</v>
       </c>
-      <c r="N15" s="49" t="s">
+      <c r="N15" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O15" s="19">
@@ -2539,7 +2569,7 @@
       <c r="M16" s="13">
         <v>10</v>
       </c>
-      <c r="N16" s="49" t="s">
+      <c r="N16" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O16" s="14">
@@ -2586,7 +2616,7 @@
       <c r="M17" s="18">
         <v>10</v>
       </c>
-      <c r="N17" s="49" t="s">
+      <c r="N17" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O17" s="19">
@@ -2631,7 +2661,7 @@
       <c r="M18" s="13">
         <v>20</v>
       </c>
-      <c r="N18" s="49" t="s">
+      <c r="N18" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O18" s="14">
@@ -2678,7 +2708,7 @@
       <c r="M19" s="18">
         <v>10</v>
       </c>
-      <c r="N19" s="49" t="s">
+      <c r="N19" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O19" s="19">
@@ -2725,7 +2755,7 @@
       <c r="M20" s="13">
         <v>5</v>
       </c>
-      <c r="N20" s="49" t="s">
+      <c r="N20" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O20" s="14">
@@ -2772,7 +2802,7 @@
       <c r="M21" s="18">
         <v>20</v>
       </c>
-      <c r="N21" s="49" t="s">
+      <c r="N21" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O21" s="19">
@@ -2819,7 +2849,7 @@
       <c r="M22" s="13">
         <v>50</v>
       </c>
-      <c r="N22" s="49" t="s">
+      <c r="N22" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O22" s="14">
@@ -2866,7 +2896,7 @@
       <c r="M23" s="18">
         <v>20</v>
       </c>
-      <c r="N23" s="49" t="s">
+      <c r="N23" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O23" s="19">
@@ -2913,7 +2943,7 @@
       <c r="M24" s="13">
         <v>5</v>
       </c>
-      <c r="N24" s="49" t="s">
+      <c r="N24" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O24" s="14">
@@ -2960,7 +2990,7 @@
       <c r="M25" s="18">
         <v>10</v>
       </c>
-      <c r="N25" s="49" t="s">
+      <c r="N25" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O25" s="19">
@@ -3007,7 +3037,7 @@
       <c r="M26" s="13">
         <v>20</v>
       </c>
-      <c r="N26" s="49" t="s">
+      <c r="N26" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O26" s="14">
@@ -3054,7 +3084,7 @@
       <c r="M27" s="18">
         <v>1</v>
       </c>
-      <c r="N27" s="49" t="s">
+      <c r="N27" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O27" s="19">
@@ -3101,7 +3131,7 @@
       <c r="M28" s="13">
         <v>3</v>
       </c>
-      <c r="N28" s="49" t="s">
+      <c r="N28" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O28" s="14">
@@ -3148,7 +3178,7 @@
       <c r="M29" s="18">
         <v>5</v>
       </c>
-      <c r="N29" s="49" t="s">
+      <c r="N29" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O29" s="19">
@@ -3195,7 +3225,7 @@
       <c r="M30" s="13">
         <v>5</v>
       </c>
-      <c r="N30" s="49" t="s">
+      <c r="N30" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O30" s="14">
@@ -3242,7 +3272,7 @@
       <c r="M31" s="18">
         <v>12</v>
       </c>
-      <c r="N31" s="49" t="s">
+      <c r="N31" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O31" s="19">
@@ -3289,7 +3319,7 @@
       <c r="M32" s="13">
         <v>5</v>
       </c>
-      <c r="N32" s="49" t="s">
+      <c r="N32" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O32" s="14">
@@ -3336,7 +3366,7 @@
       <c r="M33" s="18">
         <v>20</v>
       </c>
-      <c r="N33" s="49" t="s">
+      <c r="N33" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O33" s="19">
@@ -3383,7 +3413,7 @@
       <c r="M34" s="13">
         <v>2</v>
       </c>
-      <c r="N34" s="49" t="s">
+      <c r="N34" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O34" s="14">
@@ -3430,7 +3460,7 @@
       <c r="M35" s="18">
         <v>5</v>
       </c>
-      <c r="N35" s="49" t="s">
+      <c r="N35" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O35" s="19">
@@ -3477,7 +3507,7 @@
       <c r="M36" s="13">
         <v>5</v>
       </c>
-      <c r="N36" s="49" t="s">
+      <c r="N36" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O36" s="14">
@@ -3524,7 +3554,7 @@
       <c r="M37" s="18">
         <v>5</v>
       </c>
-      <c r="N37" s="49" t="s">
+      <c r="N37" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O37" s="19">
@@ -3571,7 +3601,7 @@
       <c r="M38" s="13">
         <v>5</v>
       </c>
-      <c r="N38" s="49" t="s">
+      <c r="N38" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O38" s="14">
@@ -3618,7 +3648,7 @@
       <c r="M39" s="18">
         <v>5</v>
       </c>
-      <c r="N39" s="49" t="s">
+      <c r="N39" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O39" s="19">
@@ -3665,7 +3695,7 @@
       <c r="M40" s="13">
         <v>5</v>
       </c>
-      <c r="N40" s="49" t="s">
+      <c r="N40" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O40" s="14">
@@ -3714,7 +3744,7 @@
       <c r="M41" s="18">
         <v>5</v>
       </c>
-      <c r="N41" s="49" t="s">
+      <c r="N41" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O41" s="19">
@@ -3763,7 +3793,7 @@
       <c r="M42" s="13">
         <v>20</v>
       </c>
-      <c r="N42" s="49" t="s">
+      <c r="N42" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O42" s="14">
@@ -3812,7 +3842,7 @@
       <c r="M43" s="18">
         <v>20</v>
       </c>
-      <c r="N43" s="49" t="s">
+      <c r="N43" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O43" s="19">
@@ -3861,7 +3891,7 @@
       <c r="M44" s="13">
         <v>100</v>
       </c>
-      <c r="N44" s="49" t="s">
+      <c r="N44" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O44" s="14">
@@ -3910,7 +3940,7 @@
       <c r="M45" s="18">
         <v>100</v>
       </c>
-      <c r="N45" s="49" t="s">
+      <c r="N45" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O45" s="19">
@@ -3959,7 +3989,7 @@
       <c r="M46" s="13">
         <v>100</v>
       </c>
-      <c r="N46" s="49" t="s">
+      <c r="N46" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O46" s="14">
@@ -4008,7 +4038,7 @@
       <c r="M47" s="18">
         <v>100</v>
       </c>
-      <c r="N47" s="49" t="s">
+      <c r="N47" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O47" s="19">
@@ -4057,7 +4087,7 @@
       <c r="M48" s="13">
         <v>50</v>
       </c>
-      <c r="N48" s="49" t="s">
+      <c r="N48" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O48" s="14">
@@ -4106,7 +4136,7 @@
       <c r="M49" s="18">
         <v>100</v>
       </c>
-      <c r="N49" s="49" t="s">
+      <c r="N49" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O49" s="19">
@@ -4155,7 +4185,7 @@
       <c r="M50" s="13">
         <v>100</v>
       </c>
-      <c r="N50" s="49" t="s">
+      <c r="N50" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O50" s="14">
@@ -4204,7 +4234,7 @@
       <c r="M51" s="18">
         <v>100</v>
       </c>
-      <c r="N51" s="49" t="s">
+      <c r="N51" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O51" s="19">
@@ -4253,7 +4283,7 @@
       <c r="M52" s="13">
         <v>20</v>
       </c>
-      <c r="N52" s="49" t="s">
+      <c r="N52" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O52" s="14">
@@ -4300,7 +4330,7 @@
       <c r="M53" s="18">
         <v>10</v>
       </c>
-      <c r="N53" s="49" t="s">
+      <c r="N53" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O53" s="19">
@@ -4347,7 +4377,7 @@
       <c r="M54" s="13">
         <v>1</v>
       </c>
-      <c r="N54" s="49" t="s">
+      <c r="N54" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O54" s="14">
@@ -4394,7 +4424,7 @@
       <c r="M55" s="18">
         <v>20</v>
       </c>
-      <c r="N55" s="49" t="s">
+      <c r="N55" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O55" s="19">
@@ -4441,7 +4471,7 @@
       <c r="M56" s="13">
         <v>1</v>
       </c>
-      <c r="N56" s="49" t="s">
+      <c r="N56" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O56" s="14">
@@ -4488,7 +4518,7 @@
       <c r="M57" s="18">
         <v>5</v>
       </c>
-      <c r="N57" s="49" t="s">
+      <c r="N57" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O57" s="19">
@@ -4535,7 +4565,7 @@
       <c r="M58" s="13">
         <v>5</v>
       </c>
-      <c r="N58" s="49" t="s">
+      <c r="N58" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O58" s="14">
@@ -4582,7 +4612,7 @@
       <c r="M59" s="18">
         <v>1</v>
       </c>
-      <c r="N59" s="49" t="s">
+      <c r="N59" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O59" s="19">
@@ -4629,7 +4659,7 @@
       <c r="M60" s="13">
         <v>5</v>
       </c>
-      <c r="N60" s="49" t="s">
+      <c r="N60" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O60" s="14">
@@ -4676,7 +4706,7 @@
       <c r="M61" s="18">
         <v>1</v>
       </c>
-      <c r="N61" s="49" t="s">
+      <c r="N61" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O61" s="19">
@@ -4723,7 +4753,7 @@
       <c r="M62" s="13">
         <v>1</v>
       </c>
-      <c r="N62" s="49" t="s">
+      <c r="N62" s="46" t="s">
         <v>339</v>
       </c>
       <c r="O62" s="14">
@@ -4745,16 +4775,16 @@
         <v>340</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F63" s="13" t="s">
         <v>332</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H63" s="13" t="s">
         <v>332</v>
@@ -4774,8 +4804,8 @@
       <c r="M63" s="13">
         <v>1</v>
       </c>
-      <c r="N63" s="49" t="s">
-        <v>348</v>
+      <c r="N63" s="46" t="s">
+        <v>347</v>
       </c>
       <c r="O63" s="14">
         <v>1.58</v>
@@ -4796,16 +4826,16 @@
         <v>340</v>
       </c>
       <c r="D64" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="E64" s="13" t="s">
         <v>349</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>350</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>332</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H64" s="13" t="s">
         <v>332</v>
@@ -4825,14 +4855,14 @@
       <c r="M64" s="13">
         <v>1</v>
       </c>
-      <c r="N64" s="49" t="s">
-        <v>348</v>
+      <c r="N64" s="46" t="s">
+        <v>347</v>
       </c>
       <c r="O64" s="14">
         <v>39.909999999999997</v>
       </c>
       <c r="P64" s="14">
-        <f t="shared" ref="P64:P65" si="28">O64*M64</f>
+        <f t="shared" ref="P64:P70" si="28">O64*M64</f>
         <v>39.909999999999997</v>
       </c>
       <c r="Q64" s="13"/>
@@ -4847,7 +4877,7 @@
         <v>340</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E65" s="13" t="s">
         <v>332</v>
@@ -4856,7 +4886,7 @@
         <v>332</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H65" s="13" t="s">
         <v>332</v>
@@ -4876,8 +4906,8 @@
       <c r="M65" s="13">
         <v>1</v>
       </c>
-      <c r="N65" s="49" t="s">
-        <v>348</v>
+      <c r="N65" s="46" t="s">
+        <v>347</v>
       </c>
       <c r="O65" s="14">
         <v>7.35</v>
@@ -4898,7 +4928,7 @@
         <v>340</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>332</v>
@@ -4907,7 +4937,7 @@
         <v>332</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H66" s="13" t="s">
         <v>332</v>
@@ -4927,13 +4957,16 @@
       <c r="M66" s="13">
         <v>1</v>
       </c>
-      <c r="N66" s="49" t="s">
+      <c r="N66" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="O66" s="14"/>
+      <c r="P66" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q66" s="47" t="s">
         <v>357</v>
-      </c>
-      <c r="O66" s="14"/>
-      <c r="P66" s="14"/>
-      <c r="Q66" s="50" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -4946,7 +4979,7 @@
         <v>340</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>332</v>
@@ -4955,7 +4988,7 @@
         <v>332</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H67" s="13" t="s">
         <v>332</v>
@@ -4975,38 +5008,41 @@
       <c r="M67" s="13">
         <v>1</v>
       </c>
-      <c r="N67" s="49" t="s">
+      <c r="N67" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="O67" s="14"/>
+      <c r="P67" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q67" s="47" t="s">
         <v>357</v>
       </c>
-      <c r="O67" s="14"/>
-      <c r="P67" s="14"/>
-      <c r="Q67" s="50" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="15">
-        <f>ROW(B68) - ROW($B$7)</f>
+      <c r="B68" s="16">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="C68" s="20" t="s">
         <v>340</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>332</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="I68" s="13" t="s">
         <v>332</v>
@@ -5018,73 +5054,206 @@
         <v>332</v>
       </c>
       <c r="L68" s="13">
+        <v>3</v>
+      </c>
+      <c r="M68" s="13">
+        <v>3</v>
+      </c>
+      <c r="N68" s="46" t="s">
+        <v>347</v>
+      </c>
+      <c r="O68" s="14">
+        <v>30.33</v>
+      </c>
+      <c r="P68" s="14">
+        <f t="shared" si="28"/>
+        <v>90.99</v>
+      </c>
+      <c r="Q68" s="47" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="16">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="L69" s="13">
         <v>1</v>
       </c>
-      <c r="M68" s="13">
-        <v>1</v>
-      </c>
-      <c r="N68" s="49" t="s">
-        <v>343</v>
-      </c>
-      <c r="O68" s="14">
-        <v>42.3</v>
-      </c>
-      <c r="P68" s="14">
-        <f>O68*M68</f>
-        <v>42.3</v>
-      </c>
-      <c r="Q68" s="13"/>
-    </row>
-    <row r="69" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="N69" s="38"/>
-      <c r="O69" s="38"/>
-      <c r="P69" s="17">
-        <f>SUM(P8:P68)</f>
-        <v>141.83609999999999</v>
-      </c>
-      <c r="Q69" s="1"/>
+      <c r="M69" s="13">
+        <v>10</v>
+      </c>
+      <c r="N69" s="46" t="s">
+        <v>339</v>
+      </c>
+      <c r="O69" s="14">
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="P69" s="14">
+        <f t="shared" si="28"/>
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="Q69" s="47"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="J71" s="1"/>
+      <c r="B70" s="16">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="46"/>
+      <c r="O70" s="14"/>
+      <c r="P70" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q70" s="47"/>
+    </row>
+    <row r="71" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="15">
+        <f>ROW(B71) - ROW($B$7)</f>
+        <v>64</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>342</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="K71" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="L71" s="13">
+        <v>1</v>
+      </c>
+      <c r="M71" s="13">
+        <v>1</v>
+      </c>
+      <c r="N71" s="46" t="s">
+        <v>369</v>
+      </c>
+      <c r="O71" s="14">
+        <v>60.87</v>
+      </c>
+      <c r="P71" s="14">
+        <f>O71*M71</f>
+        <v>60.87</v>
+      </c>
+      <c r="Q71" s="13"/>
+    </row>
+    <row r="72" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="49" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="50"/>
+      <c r="O72" s="50"/>
+      <c r="P72" s="17">
+        <f>SUM(P8:P71)</f>
+        <v>251.96009999999998</v>
+      </c>
+      <c r="Q72" s="1"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J74" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="M69:O69"/>
+    <mergeCell ref="M72:O72"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N8" r:id="rId1"/>
@@ -5142,15 +5311,17 @@
     <hyperlink ref="N60" r:id="rId53"/>
     <hyperlink ref="N61" r:id="rId54"/>
     <hyperlink ref="N62" r:id="rId55"/>
-    <hyperlink ref="N68" r:id="rId56"/>
-    <hyperlink ref="N63" r:id="rId57"/>
-    <hyperlink ref="N64" r:id="rId58"/>
-    <hyperlink ref="N65" r:id="rId59"/>
-    <hyperlink ref="N66" r:id="rId60"/>
-    <hyperlink ref="N67" r:id="rId61"/>
+    <hyperlink ref="N63" r:id="rId56"/>
+    <hyperlink ref="N64" r:id="rId57"/>
+    <hyperlink ref="N65" r:id="rId58"/>
+    <hyperlink ref="N66" r:id="rId59"/>
+    <hyperlink ref="N67" r:id="rId60"/>
+    <hyperlink ref="N69" r:id="rId61"/>
+    <hyperlink ref="N68" r:id="rId62"/>
+    <hyperlink ref="N71" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId62"/>
-  <drawing r:id="rId63"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId64"/>
+  <drawing r:id="rId65"/>
 </worksheet>
 </file>
--- a/Design Files/LogNController/BOM/eSpark BOM.xlsx
+++ b/Design Files/LogNController/BOM/eSpark BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="369">
   <si>
     <t>Component list</t>
   </si>
@@ -1086,18 +1086,6 @@
     <t>PH Sensor</t>
   </si>
   <si>
-    <t xml:space="preserve">DS380 </t>
-  </si>
-  <si>
-    <t>Disen</t>
-  </si>
-  <si>
-    <t>Supplier Quote Required</t>
-  </si>
-  <si>
-    <t>Digital pH Sensor</t>
-  </si>
-  <si>
     <t>DC Pump</t>
   </si>
   <si>
@@ -1129,6 +1117,15 @@
   </si>
   <si>
     <t>Chipsmall</t>
+  </si>
+  <si>
+    <t>Industrial Optical DO Meter Dissolved Oxygen Sensor in Water</t>
+  </si>
+  <si>
+    <t>Alibaba</t>
+  </si>
+  <si>
+    <t>Industrial RS485 Online Water ORP PH Sensor</t>
   </si>
 </sst>
 </file>
@@ -4918,7 +4915,7 @@
       </c>
       <c r="Q65" s="13"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="36" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="16">
         <f t="shared" si="0"/>
@@ -4937,7 +4934,7 @@
         <v>332</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="H66" s="13" t="s">
         <v>332</v>
@@ -4958,18 +4955,18 @@
         <v>1</v>
       </c>
       <c r="N66" s="46" t="s">
-        <v>356</v>
-      </c>
-      <c r="O66" s="14"/>
+        <v>367</v>
+      </c>
+      <c r="O66" s="14">
+        <v>125.8</v>
+      </c>
       <c r="P66" s="14">
         <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="47" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+        <v>125.8</v>
+      </c>
+      <c r="Q66" s="47"/>
+    </row>
+    <row r="67" spans="1:17" ht="24" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="16">
         <f t="shared" si="0"/>
@@ -4988,7 +4985,7 @@
         <v>332</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="H67" s="13" t="s">
         <v>332</v>
@@ -5009,16 +5006,16 @@
         <v>1</v>
       </c>
       <c r="N67" s="46" t="s">
-        <v>356</v>
-      </c>
-      <c r="O67" s="14"/>
+        <v>367</v>
+      </c>
+      <c r="O67" s="14">
+        <v>62.9</v>
+      </c>
       <c r="P67" s="14">
         <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="47" t="s">
-        <v>357</v>
-      </c>
+        <v>62.9</v>
+      </c>
+      <c r="Q67" s="47"/>
     </row>
     <row r="68" spans="1:17" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
@@ -5030,19 +5027,19 @@
         <v>340</v>
       </c>
       <c r="D68" s="13" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F68" s="13" t="s">
         <v>332</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="I68" s="13" t="s">
         <v>332</v>
@@ -5070,7 +5067,7 @@
         <v>90.99</v>
       </c>
       <c r="Q68" s="47" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -5083,19 +5080,19 @@
         <v>340</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F69" s="13" t="s">
         <v>332</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>332</v>
@@ -5134,7 +5131,7 @@
         <v>340</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
@@ -5193,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="N71" s="46" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="O71" s="14">
         <v>60.87</v>
@@ -5224,7 +5221,7 @@
       <c r="O72" s="50"/>
       <c r="P72" s="17">
         <f>SUM(P8:P71)</f>
-        <v>251.96009999999998</v>
+        <v>440.6601</v>
       </c>
       <c r="Q72" s="1"/>
     </row>
@@ -5314,11 +5311,11 @@
     <hyperlink ref="N63" r:id="rId56"/>
     <hyperlink ref="N64" r:id="rId57"/>
     <hyperlink ref="N65" r:id="rId58"/>
-    <hyperlink ref="N66" r:id="rId59"/>
-    <hyperlink ref="N67" r:id="rId60"/>
-    <hyperlink ref="N69" r:id="rId61"/>
-    <hyperlink ref="N68" r:id="rId62"/>
-    <hyperlink ref="N71" r:id="rId63"/>
+    <hyperlink ref="N69" r:id="rId59"/>
+    <hyperlink ref="N68" r:id="rId60"/>
+    <hyperlink ref="N71" r:id="rId61"/>
+    <hyperlink ref="N66" r:id="rId62"/>
+    <hyperlink ref="N67" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId64"/>
